--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2343,6 +2343,1363 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129151502</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637952</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6665553</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129151487</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96897</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>638007</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665563</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129151494</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>637901</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6665672</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129151499</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43982</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>637885</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6665599</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129151492</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92218</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>637863</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6665755</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129151496</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>637921</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6665655</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129151491</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92218</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>638007</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6665565</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129151493</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92218</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>638038</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6665703</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129151495</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>637861</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6665781</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129151488</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96897</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>53</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>637930</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6665637</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129151503</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>637885</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6665598</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129151498</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>637931</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6665656</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129151490</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>637871</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6665748</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129151489</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96897</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nötmossen Velången, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>637931</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6665640</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B25" t="n">
-        <v>96897</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R25" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>96902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R26" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91927</v>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B17" t="n">
-        <v>96902</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R17" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>96905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R18" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>96905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R25" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B26" t="n">
-        <v>96902</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R26" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91930</v>
+        <v>91933</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91488</v>
+        <v>96905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96902</v>
+        <v>91491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>96905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R17" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>96905</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R18" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B25" t="n">
-        <v>96905</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R25" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>96905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R26" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96905</v>
+        <v>91491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91491</v>
+        <v>96905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2927,7 +2927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129151491</v>
+        <v>129151493</v>
       </c>
       <c r="B22" t="n">
         <v>92226</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638007</v>
+        <v>638038</v>
       </c>
       <c r="R22" t="n">
-        <v>6665565</v>
+        <v>6665703</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129151493</v>
+        <v>129151491</v>
       </c>
       <c r="B23" t="n">
         <v>92226</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638038</v>
+        <v>638007</v>
       </c>
       <c r="R23" t="n">
-        <v>6665703</v>
+        <v>6665565</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>96905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R25" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B26" t="n">
-        <v>96905</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R26" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91491</v>
+        <v>96905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96905</v>
+        <v>91491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129151496</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129151493</v>
+        <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638038</v>
+        <v>638007</v>
       </c>
       <c r="R22" t="n">
-        <v>6665703</v>
+        <v>6665565</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129151491</v>
+        <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638007</v>
+        <v>638038</v>
       </c>
       <c r="R23" t="n">
-        <v>6665565</v>
+        <v>6665703</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3124,7 +3124,7 @@
         <v>129151495</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91933</v>
+        <v>91940</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91940</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129151496</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>129151495</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B25" t="n">
-        <v>96922</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R25" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>96924</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R26" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96922</v>
+        <v>91506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91504</v>
+        <v>96924</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B17" t="n">
-        <v>96924</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R17" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>96924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R18" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>96924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R25" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B26" t="n">
-        <v>96924</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R26" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91506</v>
+        <v>96924</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96924</v>
+        <v>91506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>96950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R17" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>96924</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R18" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91949</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96924</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91506</v>
+        <v>96950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B17" t="n">
-        <v>96952</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R17" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>96956</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R18" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>96956</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96952</v>
+        <v>91507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>96956</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R17" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>96956</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R18" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91961</v>
+        <v>91963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91963</v>
+        <v>91967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91967</v>
+        <v>91968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96962</v>
+        <v>91514</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91513</v>
+        <v>96970</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B25" t="n">
-        <v>96970</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R25" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>96970</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R26" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91514</v>
+        <v>96970</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96970</v>
+        <v>91514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96970</v>
+        <v>91514</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91514</v>
+        <v>96970</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3218,32 +3218,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151503</v>
+        <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>96973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637885</v>
+        <v>637930</v>
       </c>
       <c r="R25" t="n">
-        <v>6665598</v>
+        <v>6665637</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151488</v>
+        <v>129151503</v>
       </c>
       <c r="B26" t="n">
-        <v>96970</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637930</v>
+        <v>637885</v>
       </c>
       <c r="R26" t="n">
-        <v>6665637</v>
+        <v>6665598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91968</v>
+        <v>91971</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91517</v>
+        <v>96973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96973</v>
+        <v>91517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B17" t="n">
-        <v>96973</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R17" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>96973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R18" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151494</v>
+        <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>96973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2453,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637901</v>
+        <v>638007</v>
       </c>
       <c r="R17" t="n">
-        <v>6665672</v>
+        <v>6665563</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>96973</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R18" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B28" t="n">
-        <v>96973</v>
+        <v>91517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B29" t="n">
-        <v>91517</v>
+        <v>96973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2927,7 +2927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129151491</v>
+        <v>129151493</v>
       </c>
       <c r="B22" t="n">
         <v>92271</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638007</v>
+        <v>638038</v>
       </c>
       <c r="R22" t="n">
-        <v>6665565</v>
+        <v>6665703</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129151493</v>
+        <v>129151491</v>
       </c>
       <c r="B23" t="n">
         <v>92271</v>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638038</v>
+        <v>638007</v>
       </c>
       <c r="R23" t="n">
-        <v>6665703</v>
+        <v>6665565</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -2445,7 +2445,7 @@
         <v>129151487</v>
       </c>
       <c r="B17" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129151494</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>129151499</v>
       </c>
       <c r="B19" t="n">
-        <v>43982</v>
+        <v>43985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129151492</v>
       </c>
       <c r="B20" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129151496</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129151493</v>
+        <v>129151491</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638038</v>
+        <v>638007</v>
       </c>
       <c r="R22" t="n">
-        <v>6665703</v>
+        <v>6665565</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129151491</v>
+        <v>129151493</v>
       </c>
       <c r="B23" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638007</v>
+        <v>638038</v>
       </c>
       <c r="R23" t="n">
-        <v>6665565</v>
+        <v>6665703</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3124,7 +3124,7 @@
         <v>129151495</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129151488</v>
       </c>
       <c r="B25" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129151498</v>
       </c>
       <c r="B27" t="n">
-        <v>91971</v>
+        <v>91999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,32 +3508,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151490</v>
+        <v>129151489</v>
       </c>
       <c r="B28" t="n">
-        <v>91517</v>
+        <v>97002</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R28" t="n">
-        <v>6665748</v>
+        <v>6665640</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3605,32 +3605,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151489</v>
+        <v>129151490</v>
       </c>
       <c r="B29" t="n">
-        <v>96973</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637931</v>
+        <v>637871</v>
       </c>
       <c r="R29" t="n">
-        <v>6665640</v>
+        <v>6665748</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>

--- a/artfynd/A 48755-2025 artfynd.xlsx
+++ b/artfynd/A 48755-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124190637</v>
+        <v>124205123</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637893</v>
+        <v>637929</v>
       </c>
       <c r="R2" t="n">
-        <v>6665652</v>
+        <v>6665530</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +790,7 @@
         <v>124232392</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124209310</v>
+        <v>129151487</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638018</v>
+        <v>638007</v>
       </c>
       <c r="R4" t="n">
-        <v>6665626</v>
+        <v>6665563</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,27 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>9 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,27 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189769</v>
+        <v>129151488</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,45 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638030</v>
+        <v>637930</v>
       </c>
       <c r="R5" t="n">
-        <v>6665602</v>
+        <v>6665637</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,69 +1071,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189300</v>
+        <v>129151489</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638050</v>
+        <v>637931</v>
       </c>
       <c r="R6" t="n">
-        <v>6665625</v>
+        <v>6665640</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,27 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett par bladrosetter invid körspår</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,34 +1162,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124232011</v>
+        <v>124204041</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1210,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,14 +1227,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Hällholmen, söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638028</v>
+        <v>637921</v>
       </c>
       <c r="R7" t="n">
-        <v>6665609</v>
+        <v>6665671</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,14 +1264,24 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På murken stubbe i granskog</t>
+          <t>2 kapslar på murken stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,57 +1309,64 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124205123</v>
+        <v>124232011</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637929</v>
+        <v>638028</v>
       </c>
       <c r="R8" t="n">
-        <v>6665530</v>
+        <v>6665609</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1464,19 +1393,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:25</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På murken stubbe i granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,15 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124204041</v>
+        <v>129151491</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,53 +1439,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällholmen, söder om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637921</v>
+        <v>638007</v>
       </c>
       <c r="R9" t="n">
-        <v>6665671</v>
+        <v>6665565</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,27 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 kapslar på murken stubbe</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,76 +1507,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124189873</v>
+        <v>129151492</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638016</v>
+        <v>637863</v>
       </c>
       <c r="R10" t="n">
-        <v>6665594</v>
+        <v>6665755</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,27 +1590,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Cirka 10 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,76 +1604,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124204400</v>
+        <v>129151493</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637987</v>
+        <v>638038</v>
       </c>
       <c r="R11" t="n">
-        <v>6665598</v>
+        <v>6665703</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,27 +1687,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,76 +1701,66 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124205801</v>
+        <v>129151490</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637878</v>
+        <v>637871</v>
       </c>
       <c r="R12" t="n">
-        <v>6665615</v>
+        <v>6665748</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,27 +1784,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,71 +1798,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124698226</v>
+        <v>129151495</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638166</v>
+        <v>637861</v>
       </c>
       <c r="R13" t="n">
-        <v>6665714</v>
+        <v>6665781</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,27 +1881,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,67 +1895,66 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124696996</v>
+        <v>129151496</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nötmossen, norr om, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638100</v>
+        <v>637921</v>
       </c>
       <c r="R14" t="n">
-        <v>6665721</v>
+        <v>6665655</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,27 +1978,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,60 +1998,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124697608</v>
+        <v>129151499</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>44177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nötmossen, Upl</t>
+          <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638131</v>
+        <v>637885</v>
       </c>
       <c r="R15" t="n">
-        <v>6665719</v>
+        <v>6665599</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2298,27 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Mer än 30 bladrosetter</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,60 +2095,68 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129151502</v>
+        <v>124189769</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>637952</v>
+        <v>638030</v>
       </c>
       <c r="R16" t="n">
-        <v>6665553</v>
+        <v>6665602</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2410,12 +2180,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,22 +2210,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129151487</v>
+        <v>129151494</v>
       </c>
       <c r="B17" t="n">
-        <v>97002</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638007</v>
+        <v>637901</v>
       </c>
       <c r="R17" t="n">
-        <v>6665563</v>
+        <v>6665672</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2539,32 +2319,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129151494</v>
+        <v>129151502</v>
       </c>
       <c r="B18" t="n">
-        <v>57890</v>
+        <v>8444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637901</v>
+        <v>637952</v>
       </c>
       <c r="R18" t="n">
-        <v>6665672</v>
+        <v>6665553</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2636,10 +2416,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129151499</v>
+        <v>129151503</v>
       </c>
       <c r="B19" t="n">
-        <v>43985</v>
+        <v>8444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2674,7 +2454,7 @@
         <v>637885</v>
       </c>
       <c r="R19" t="n">
-        <v>6665599</v>
+        <v>6665598</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2733,48 +2513,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129151492</v>
+        <v>124189300</v>
       </c>
       <c r="B20" t="n">
-        <v>92299</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637863</v>
+        <v>638050</v>
       </c>
       <c r="R20" t="n">
-        <v>6665755</v>
+        <v>6665625</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2798,12 +2582,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ett par bladrosetter invid körspår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,66 +2611,71 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129151496</v>
+        <v>124189873</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637921</v>
+        <v>638016</v>
       </c>
       <c r="R21" t="n">
-        <v>6665655</v>
+        <v>6665594</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,12 +2699,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Cirka 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,66 +2728,71 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129151491</v>
+        <v>124190637</v>
       </c>
       <c r="B22" t="n">
-        <v>92299</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638007</v>
+        <v>637893</v>
       </c>
       <c r="R22" t="n">
-        <v>6665565</v>
+        <v>6665652</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2992,12 +2816,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,66 +2845,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129151493</v>
+        <v>124204400</v>
       </c>
       <c r="B23" t="n">
-        <v>92299</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638038</v>
+        <v>637987</v>
       </c>
       <c r="R23" t="n">
-        <v>6665703</v>
+        <v>6665598</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3089,12 +2933,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,66 +2962,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129151495</v>
+        <v>124205801</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>637861</v>
+        <v>637878</v>
       </c>
       <c r="R24" t="n">
-        <v>6665781</v>
+        <v>6665615</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3186,12 +3050,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,66 +3079,67 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129151488</v>
+        <v>124209310</v>
       </c>
       <c r="B25" t="n">
-        <v>97002</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637930</v>
+        <v>638018</v>
       </c>
       <c r="R25" t="n">
-        <v>6665637</v>
+        <v>6665626</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3283,12 +3163,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>9 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3303,60 +3198,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129151503</v>
+        <v>124696996</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, norr om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637885</v>
+        <v>638100</v>
       </c>
       <c r="R26" t="n">
-        <v>6665598</v>
+        <v>6665721</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3380,12 +3275,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,58 +3310,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129151498</v>
+        <v>124697608</v>
       </c>
       <c r="B27" t="n">
-        <v>91999</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>637931</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>6665656</v>
+        <v>6665719</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3475,12 +3387,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mer än 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,67 +3416,70 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129151489</v>
+        <v>124698226</v>
       </c>
       <c r="B28" t="n">
-        <v>97002</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nötmossen Velången, Upl</t>
+          <t>Nötmossen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637931</v>
+        <v>638166</v>
       </c>
       <c r="R28" t="n">
-        <v>6665640</v>
+        <v>6665714</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,12 +3503,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,63 +3532,67 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129151490</v>
+        <v>129151498</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>92328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6040162</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nötmossen Velången, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637871</v>
+        <v>637931</v>
       </c>
       <c r="R29" t="n">
-        <v>6665748</v>
+        <v>6665656</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3684,6 +3633,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
